--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
@@ -4476,7 +4476,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
@@ -4476,7 +4476,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
@@ -5248,7 +5248,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
@@ -4476,7 +4476,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
@@ -4476,7 +4476,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
@@ -4476,7 +4476,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
@@ -4476,7 +4476,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
@@ -4476,7 +4476,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
@@ -4476,7 +4476,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251123_201444.xlsx
@@ -4476,7 +4476,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
